--- a/content/events.xlsx
+++ b/content/events.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -27,6 +27,9 @@
     <t>stat</t>
   </si>
   <si>
+    <t>statName</t>
+  </si>
+  <si>
     <t>gain</t>
   </si>
   <si>
@@ -39,6 +42,9 @@
     <t>dance</t>
   </si>
   <si>
+    <t>舞蹈</t>
+  </si>
+  <si>
     <t>r-convenience</t>
   </si>
   <si>
@@ -57,6 +63,9 @@
     <t>vocal</t>
   </si>
   <si>
+    <t>演唱</t>
+  </si>
+  <si>
     <t>r-note</t>
   </si>
   <si>
@@ -66,6 +75,9 @@
     <t>acting</t>
   </si>
   <si>
+    <t>演技</t>
+  </si>
+  <si>
     <t>r-tired</t>
   </si>
   <si>
@@ -79,6 +91,9 @@
   </si>
   <si>
     <t>talk</t>
+  </si>
+  <si>
+    <t>口才</t>
   </si>
   <si>
     <t>r-rain</t>
@@ -689,16 +704,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -714,208 +731,247 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>-3</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>-1</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>-2</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>-2</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>-1</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>-2</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>-1</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
     </row>
@@ -941,101 +997,101 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1065,13 +1121,13 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -1080,42 +1136,42 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>-10</v>
@@ -1130,33 +1186,33 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E3">
         <v>-5</v>
@@ -1165,42 +1221,42 @@
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>5</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>-6</v>
@@ -1209,39 +1265,39 @@
         <v>-2</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1250,77 +1306,77 @@
         <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>40</v>
@@ -1329,39 +1385,39 @@
         <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E8">
         <v>-5</v>
@@ -1370,39 +1426,39 @@
         <v>-5</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1414,45 +1470,45 @@
         <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -1461,30 +1517,30 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -1496,36 +1552,36 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>-5</v>
@@ -1540,19 +1596,19 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
